--- a/dataset/mol_list.xlsx
+++ b/dataset/mol_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
     <t>InChIKey</t>
   </si>
@@ -34,12 +34,24 @@
     <t>C#CC(C)=O</t>
   </si>
   <si>
+    <t>FUSUHKVFWTUUBE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C=CC(C)=O</t>
+  </si>
+  <si>
     <t>ZWEHNKRNPOVVGH-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCC(C)=O</t>
   </si>
   <si>
+    <t>ZTQSAGDEMFDKMZ-QYKNYGDISA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)CCC</t>
+  </si>
+  <si>
     <t>MSWVMWGCNZQPIA-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -52,6 +64,12 @@
     <t>O=C1C=CCC1</t>
   </si>
   <si>
+    <t>LABTWGUMFABVFG-ONEGZZNKSA-N</t>
+  </si>
+  <si>
+    <t>C/C=C/C(C)=O</t>
+  </si>
+  <si>
     <t>HVCFCNAITDHQFX-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -76,46 +94,64 @@
     <t>CC(=O)C(F)F</t>
   </si>
   <si>
+    <t>KLQCAVMGXXCQHN-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)C(C)C</t>
+  </si>
+  <si>
     <t>FWFSEYBSWVRWGL-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C1C=CCCC1</t>
   </si>
   <si>
-    <t>SHOJXDKTYKFBRD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C=C(C)C</t>
-  </si>
-  <si>
     <t>UOTSYAILGSUTAC-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>C=C(CC)C(C)=O</t>
   </si>
   <si>
+    <t>QQZOPKMRPOGIEB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(C)=O</t>
+  </si>
+  <si>
     <t>PJGSXYOJTGTZAV-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)C(C)(C)C</t>
   </si>
   <si>
-    <t>QQZOPKMRPOGIEB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(C)=O</t>
-  </si>
-  <si>
-    <t>VFPKIWATTACVJR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CN(C)C</t>
-  </si>
-  <si>
-    <t>IEMMBWWQXVXBEU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccco1</t>
+    <t>LTNUSYNQZJZUSY-UICOGKGYSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)CC(C)(C)C</t>
+  </si>
+  <si>
+    <t>CWKLZLBVOJRSOM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)C(C)=O</t>
+  </si>
+  <si>
+    <t>HUMNYLRZRPPJDN-RAMDWTOOSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>IITQJMYAYSNIMI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1=CC(=O)CCC1</t>
+  </si>
+  <si>
+    <t>KPMKEVXVVHNIEY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CC2CCC1C2</t>
   </si>
   <si>
     <t>LKTNAAYQZJAXCJ-UHFFFAOYSA-N</t>
@@ -136,58 +172,52 @@
     <t>CC(=O)C(F)(F)F</t>
   </si>
   <si>
+    <t>UJBOOUHRTQVGRU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1CCCC(=O)C1</t>
+  </si>
+  <si>
+    <t>LFSAPCRASZRSKS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1CCCCC1=O</t>
+  </si>
+  <si>
+    <t>FTGZMZBYOHMEPS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1(C)CCCC1=O</t>
+  </si>
+  <si>
     <t>LKENTYLPIUIMFG-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)C1CCCC1</t>
   </si>
   <si>
-    <t>FTGZMZBYOHMEPS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC1(C)CCCC1=O</t>
-  </si>
-  <si>
     <t>XXRCUYVCPSWGCC-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCOC(=O)C(C)=O</t>
   </si>
   <si>
-    <t>ULVSHNOGEVXRDR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(OC)C(C)=O</t>
-  </si>
-  <si>
     <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>WMQUKDQWMMOHSA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccncc1</t>
-  </si>
-  <si>
-    <t>AJKVQEKCUACUMD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccn1</t>
-  </si>
-  <si>
     <t>WEGYGNROSJDEIW-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)c1cccnc1</t>
   </si>
   <si>
-    <t>HDURLXYBKGWETC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C1=C(C)CCC1</t>
+    <t>OIWBNCGEFFHTNG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)CCCCC</t>
   </si>
   <si>
     <t>LTYLUDGDHUEBGX-UHFFFAOYSA-N</t>
@@ -196,6 +226,12 @@
     <t>CC(=O)C1=CCCCC1</t>
   </si>
   <si>
+    <t>QKYJXFWNIYQOJZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C#CC(C)(C)C</t>
+  </si>
+  <si>
     <t>CSVFWMMPUJDVKH-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -208,10 +244,10 @@
     <t>CC(=O)c1cccs1</t>
   </si>
   <si>
-    <t>RNIDWJDZNNVFDY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccsc1</t>
+    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C1CCCCC1</t>
   </si>
   <si>
     <t>KNSPBSQWRKKAPI-UHFFFAOYSA-N</t>
@@ -220,36 +256,42 @@
     <t>CC1(C)CCCCC1=O</t>
   </si>
   <si>
-    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>VJQKJGLHKJYTQM-SNAWJCMRSA-N</t>
-  </si>
-  <si>
-    <t>C/C=C/C(=O)CC(C)C</t>
-  </si>
-  <si>
-    <t>MOMFXATYAINJML-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1nccs1</t>
-  </si>
-  <si>
     <t>ZPVFWPFBNIEHGJ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCC(C)=O</t>
   </si>
   <si>
+    <t>WUBJISGMPZWFKY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(=O)OC(C)C</t>
+  </si>
+  <si>
+    <t>MBNLVYPIKSWXCT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)C(=O)OC</t>
+  </si>
+  <si>
+    <t>NKWVBPZZQFOVCE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)C(=O)C(C)C</t>
+  </si>
+  <si>
     <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C1CCc2ccccc21</t>
   </si>
   <si>
+    <t>KJPRLNWUNMBNBZ-NAEVNASTSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)/C=C/c1ccccc1</t>
+  </si>
+  <si>
     <t>QCCDLTOVEPVEJK-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -274,16 +316,10 @@
     <t>CCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>FSPSELPMWGWDRY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccc(C)c1</t>
-  </si>
-  <si>
-    <t>GPRYKVSEZCQIHD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(N)cc1</t>
+    <t>HEQOJEGTZCTHCF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>NCC(=O)c1ccccc1</t>
   </si>
   <si>
     <t>VRZSUVFVIIVLPV-UHFFFAOYSA-N</t>
@@ -292,28 +328,28 @@
     <t>C#CC(=O)C1CCCCC1</t>
   </si>
   <si>
+    <t>ZRSNZINYAWTAHE-RAMDWTOOSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)c1ccc(OC)cc1</t>
+  </si>
+  <si>
+    <t>ZDPAWHACYDRYIW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc(F)cc1</t>
+  </si>
+  <si>
     <t>YOMBUJAFGMOIGS-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(CF)c1ccccc1</t>
   </si>
   <si>
-    <t>HCEKGPAHZCYRBZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccc(F)c1</t>
-  </si>
-  <si>
-    <t>QMATYTFXDIWACW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1F</t>
-  </si>
-  <si>
-    <t>ZDPAWHACYDRYIW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(F)cc1</t>
+    <t>GSSRLAIHCZNDAA-SOFGYWHQSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)/C=C1\CCCC1=O</t>
   </si>
   <si>
     <t>QRYJGVNQNLCGGZ-UHFFFAOYSA-N</t>
@@ -322,16 +358,10 @@
     <t>O=C1CCCC12CCCC2</t>
   </si>
   <si>
-    <t>GSSRLAIHCZNDAA-SOFGYWHQSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)/C=C1\CCCC1=O</t>
-  </si>
-  <si>
-    <t>CZSBBWHUCQLKNQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C1=CCCCCC1</t>
+    <t>NGLHQHAKQILQGD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C#CC(C)=O</t>
   </si>
   <si>
     <t>AMHOPTNGSNYSBL-UHFFFAOYSA-N</t>
@@ -340,10 +370,10 @@
     <t>CCC(=O)C1CCCCC1</t>
   </si>
   <si>
-    <t>HDKLIZDXVUCLHQ-BQYQJAHWSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC/C=C/C(C)=O</t>
+    <t>AVPYQKSLYISFPO-UICOGKGYSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)c1ccc(Cl)cc1</t>
   </si>
   <si>
     <t>RRJHAIWETICRET-UHFFFAOYSA-N</t>
@@ -352,6 +382,12 @@
     <t>CCCCC#CC(=O)CF</t>
   </si>
   <si>
+    <t>NACDWFXPFSCTPL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)CN</t>
+  </si>
+  <si>
     <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -364,6 +400,18 @@
     <t>CCOC(=O)CCC(C)=O</t>
   </si>
   <si>
+    <t>YERWBBMSDMSDKT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)C(=O)OCC</t>
+  </si>
+  <si>
+    <t>YVZKICWRYOHMRD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(=O)OC(C)(C)C</t>
+  </si>
+  <si>
     <t>FNENWZWNOPCZGK-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -388,10 +436,10 @@
     <t>CC(=O)/C=C/c1ccccc1</t>
   </si>
   <si>
-    <t>PJRHFTYXYCVOSJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C1CC1</t>
+    <t>ULGQTMJOCRMHRB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)CF</t>
   </si>
   <si>
     <t>MSTDXOZUKAQDRL-UHFFFAOYSA-N</t>
@@ -400,34 +448,40 @@
     <t>O=C1CCOc2ccccc21</t>
   </si>
   <si>
+    <t>FFSAXUULYPJSKH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>AKGGYBADQZYZPD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)CCc1ccccc1</t>
+  </si>
+  <si>
     <t>BSMGLVDZZMBWQB-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(C)C(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>HSDSKVWQTONQBJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C)cc1C</t>
-  </si>
-  <si>
-    <t>AKGGYBADQZYZPD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CCc1ccccc1</t>
-  </si>
-  <si>
-    <t>FFSAXUULYPJSKH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>OPPJOYDMQXHCFS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)c1ccccn1</t>
+    <t>FUFAHIJREMQVPV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cc1ccc(C(=O)CN)cc1</t>
+  </si>
+  <si>
+    <t>OCHREGYEOMPRIT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cc1cccc(C(=O)CN)c1</t>
+  </si>
+  <si>
+    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(C)=O)c1</t>
   </si>
   <si>
     <t>DWPLEOPKBWNPQV-UHFFFAOYSA-N</t>
@@ -436,18 +490,6 @@
     <t>COc1ccccc1C(C)=O</t>
   </si>
   <si>
-    <t>QWAVNXZAQASOML-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)COc1ccccc1</t>
-  </si>
-  <si>
-    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1cccc(C(C)=O)c1</t>
-  </si>
-  <si>
     <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -472,10 +514,10 @@
     <t>O=C1CCN2C(=O)CCC=C12</t>
   </si>
   <si>
-    <t>RPMOHVRRKYJFSB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1cccc(F)c1</t>
+    <t>BXRFQSNOROATLV-UICOGKGYSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)c1ccc([N+](=O)[O-])cc1</t>
   </si>
   <si>
     <t>UWEKKSOZSXKQOQ-UHFFFAOYSA-N</t>
@@ -484,22 +526,16 @@
     <t>C#CC(=O)CCCCCCC</t>
   </si>
   <si>
-    <t>ZDOYHCIRUPHUHN-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1Cl</t>
-  </si>
-  <si>
     <t>IMACFCSSMIZSPP-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(CCl)c1ccccc1</t>
   </si>
   <si>
-    <t>FGGKJHHNBUNROM-SNAWJCMRSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)/C=C/C1=[SH]C=CC1</t>
+    <t>SBMVKNANFYRAHL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C#CC(=O)CC</t>
   </si>
   <si>
     <t>UYMHLXHLPQIDMA-UHFFFAOYSA-N</t>
@@ -508,12 +544,6 @@
     <t>CCCC(=O)C1CCCCC1</t>
   </si>
   <si>
-    <t>QEWHNJPLPZOEKU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(F)cc1F</t>
-  </si>
-  <si>
     <t>OLYKCPDTXVZOQF-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -532,12 +562,24 @@
     <t>CCC(=O)C#Cc1ccccc1</t>
   </si>
   <si>
+    <t>WQRUFMHFJXVZMZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCC(=O)C(=O)OC(C)(C)C</t>
+  </si>
+  <si>
     <t>NVAHZHOCRQCUBY-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCOC(=O)C(C)(C)C(C)=O</t>
   </si>
   <si>
+    <t>MGSWAHQQBHNCEI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(=O)CC(C)C</t>
+  </si>
+  <si>
     <t>SMZHKGXSEAGRTI-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -568,28 +610,22 @@
     <t>O=C(C#Cc1ccccc1)CF</t>
   </si>
   <si>
+    <t>OECPUBRNDKXFDX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)C(=O)c1ccccc1</t>
+  </si>
+  <si>
     <t>XKGLSKVNOSHTAD-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>OECPUBRNDKXFDX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>UMLWXYJZDNNBTD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CN(C)CC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>SLOCEDWZEACARV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CN(C)c1ccccc1</t>
+    <t>NNTPEAXKKUPBHQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)C(=O)CBr</t>
   </si>
   <si>
     <t>CVQSWZMJOGOPAV-UHFFFAOYSA-N</t>
@@ -604,46 +640,34 @@
     <t>COC(=O)C(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>AFTUQMXNVYPAJO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C=CCCCC(=O)c1ccco1</t>
-  </si>
-  <si>
     <t>FHIOYMGCAXTUGF-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>COc1ccc(C)cc1C(C)=O</t>
   </si>
   <si>
+    <t>PFOYLZWXMOUFRP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C(F)F</t>
+  </si>
+  <si>
     <t>FFZLOJDYTNKOCQ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>C=CC1=C(C)C(=O)CCC1(C)C</t>
   </si>
   <si>
-    <t>YQYGPGKTNQNXMH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc([N+](=O)[O-])cc1</t>
-  </si>
-  <si>
     <t>ZMOYCFVCHCPLPQ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C1CCN2C(=O)CCCC=C12</t>
   </si>
   <si>
-    <t>YUAYWSBSIJVIBS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCC(=O)c1ccco1</t>
-  </si>
-  <si>
-    <t>PQWGFUFROKIJBO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1cccc(Cl)c1</t>
+    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCCl)c1ccccc1</t>
   </si>
   <si>
     <t>ADCYRBXQAJXJTD-UHFFFAOYSA-N</t>
@@ -652,12 +676,6 @@
     <t>CCC(=O)c1ccc(Cl)cc1</t>
   </si>
   <si>
-    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCCl)c1ccccc1</t>
-  </si>
-  <si>
     <t>CNVGMLMIQIPAFY-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -670,6 +688,12 @@
     <t>CCCCC(=O)C1CCCCC1</t>
   </si>
   <si>
+    <t>VDSDKOOEBXFJCU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>NCC(=O)c1ccccc1Cl</t>
+  </si>
+  <si>
     <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -694,12 +718,24 @@
     <t>O=C1CCC/C1=C\c1ccccc1</t>
   </si>
   <si>
+    <t>WUUPUVDFXNZZPO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC#CC(=O)C(C)c1ccccc1</t>
+  </si>
+  <si>
     <t>AOOHPXMHKBITKB-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(C)C(=O)C#Cc1ccccc1</t>
   </si>
   <si>
+    <t>RKWJIFVZULBMHX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)C(=O)OC(C)(C)C</t>
+  </si>
+  <si>
     <t>KYNHSQQWQIIFTG-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -712,16 +748,16 @@
     <t>O=C(c1ccccc1)C(F)(F)F</t>
   </si>
   <si>
-    <t>CAXIQKXPSQYDIR-CMDGGOBGSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)/C=C/c1ccccc1</t>
-  </si>
-  <si>
-    <t>MQESVSITPLILCO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCc1ccc(C(C)=O)cc1</t>
+    <t>SGSGCQGCVKWRNM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cc2ccccc2s1</t>
+  </si>
+  <si>
+    <t>ZTTZKDDWXHQKSY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1csc2ccccc12</t>
   </si>
   <si>
     <t>DYQAZJQDLPPHNB-UHFFFAOYSA-N</t>
@@ -730,16 +766,10 @@
     <t>CCCCC(=O)Cc1ccccc1</t>
   </si>
   <si>
-    <t>YSZGCNKBKQQPAH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)Nc1ccccc1C(C)=O</t>
-  </si>
-  <si>
-    <t>QMNXJNURJISYMS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CN(C)CCC(=O)c1ccccc1</t>
+    <t>ARUJVOKREAIMBP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)COc1ccc(F)cc1</t>
   </si>
   <si>
     <t>XAXKYUYIYBKVHR-UHFFFAOYSA-N</t>
@@ -748,16 +778,22 @@
     <t>CCCCC#CC(=O)C(F)(F)F</t>
   </si>
   <si>
+    <t>QKLCQKPAECHXCQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(=O)c1ccccc1</t>
+  </si>
+  <si>
     <t>UFOAYTOVTNNRKJ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>COC(=O)c1ccccc1C(C)=O</t>
   </si>
   <si>
-    <t>QKLCQKPAECHXCQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)C(=O)c1ccccc1</t>
+    <t>DNHDRUMZDHWHKG-NSHDSACASA-N</t>
+  </si>
+  <si>
+    <t>C[C@]12CCC(=O)C=C1CCCC2=O</t>
   </si>
   <si>
     <t>SCDHTAAYEHJTGD-UHFFFAOYSA-N</t>
@@ -790,40 +826,40 @@
     <t>COc1ccc(OC)c(C(C)=O)c1</t>
   </si>
   <si>
+    <t>IQZLUWLMQNGTIW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc(C(C)=O)cc1OC</t>
+  </si>
+  <si>
     <t>XEUGKOFTNAYMMX-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>COc1cccc(OC)c1C(C)=O</t>
   </si>
   <si>
-    <t>IQZLUWLMQNGTIW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(C)=O)cc1OC</t>
-  </si>
-  <si>
     <t>FODUVZQSLRHUMC-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>COc1cccc(C(C)=O)c1OC</t>
   </si>
   <si>
-    <t>GCSHUYKULREZSJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccccn1</t>
-  </si>
-  <si>
-    <t>RYMBAPVTUHZCNF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1cccnc1</t>
-  </si>
-  <si>
-    <t>SKFLCXNDKRUHTA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccncc1</t>
+    <t>PMKRXALCEGXVNW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC#CC(=O)CCC</t>
+  </si>
+  <si>
+    <t>FDVRWEJPVWVEDC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)CCCCC</t>
+  </si>
+  <si>
+    <t>DPXNESFWZZBKJM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C(F)(F)F</t>
   </si>
   <si>
     <t>MCRINSAETDOKDE-UHFFFAOYSA-N</t>
@@ -832,10 +868,10 @@
     <t>COc1ccc(C(=O)CCl)cc1</t>
   </si>
   <si>
-    <t>RRRLNSBRKAMGPF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CN(C)CCC(=O)C1=[SH]C=CC1</t>
+    <t>HSFBJUJAIDNREV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)c1ccccc1</t>
   </si>
   <si>
     <t>QXGIWMOPVOXYCX-UHFFFAOYSA-N</t>
@@ -850,10 +886,10 @@
     <t>O=C1CCCC/C1=C\c1ccccc1</t>
   </si>
   <si>
-    <t>XMCRWEBERCXJCH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(Cl)cc1Cl</t>
+    <t>IPRZICNDWOSMIL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)CC(=O)C(=O)OC(C)(C)C</t>
   </si>
   <si>
     <t>CERJZAHSUZVMCH-UHFFFAOYSA-N</t>
@@ -868,24 +904,6 @@
     <t>CC1=C(Br)C(=O)CCC1</t>
   </si>
   <si>
-    <t>HHAISVSEJFEWBZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C(F)(F)F)cc1</t>
-  </si>
-  <si>
-    <t>ABXGMGUHGLQMAW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccc(C(F)(F)F)c1</t>
-  </si>
-  <si>
-    <t>FYDUUODXZQITBF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1C(F)(F)F</t>
-  </si>
-  <si>
     <t>BMFYCFSWWDXEPB-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -904,10 +922,10 @@
     <t>CCCCC(=O)CCc1ccccc1</t>
   </si>
   <si>
-    <t>WILPNXBAEMGDCS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)N(C)CC(=O)c1ccccc1</t>
+    <t>OPFNZXZQKMKHQZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)OC(=O)C(=O)c1ccccc1</t>
   </si>
   <si>
     <t>PJVVSYKDAYJZCV-UHFFFAOYSA-N</t>
@@ -922,18 +940,18 @@
     <t>COC(=O)CCC(=O)c1ccccc1</t>
   </si>
   <si>
+    <t>MSRORZBOBVAASL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)C(=O)C#CC1CCCCC1</t>
+  </si>
+  <si>
     <t>PSQYTAPXSHCGMF-BQYQJAHWSA-N</t>
   </si>
   <si>
     <t>CC(=O)/C=C/C1=C(C)CCCC1(C)C</t>
   </si>
   <si>
-    <t>MSRORZBOBVAASL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)C(=O)C#CC1CCCCC1</t>
-  </si>
-  <si>
     <t>DKVCHMQHUMLKPO-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -946,54 +964,24 @@
     <t>CCCCCCC/C=C1\CCCC1=O</t>
   </si>
   <si>
+    <t>CKGKXGQVRVAKEA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cc1ccccc1C(=O)c1ccccc1</t>
+  </si>
+  <si>
     <t>OTKCEEWUXHVZQI-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(Cc1ccccc1)c1ccccc1</t>
   </si>
   <si>
-    <t>WXPWZZHELZEVPO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C(=O)c2ccccc2)cc1</t>
-  </si>
-  <si>
-    <t>CKGKXGQVRVAKEA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccccc1C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>QCZZSANNLWPGEA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(-c2ccccc2)cc1</t>
-  </si>
-  <si>
     <t>NDQOKFMZSIKVBG-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCC(=O)C(F)(F)F</t>
   </si>
   <si>
-    <t>BHDAKOZHMSQCFH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C(=O)c2ccccn2)cc1</t>
-  </si>
-  <si>
-    <t>YIPODLIDWSBPJA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccccc1C(=O)c1cccnc1</t>
-  </si>
-  <si>
-    <t>CXDYOXSPZUWEQX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C(=O)c2cccnc2)cc1</t>
-  </si>
-  <si>
     <t>JYAQYXOVOHJRCS-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1048,16 +1036,28 @@
     <t>COc1ccc2cc(C(C)=O)ccc2c1</t>
   </si>
   <si>
+    <t>XGUAEEGZGYIHBV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C#CC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>OAWLQFAFOVHFEE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)CCCOCc1ccccc1</t>
+  </si>
+  <si>
     <t>NHBBLULITNXPDY-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(Cc1ccccc1)C1CCCCC1</t>
   </si>
   <si>
-    <t>NCJZVRPXSSYDBG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(=O)C(F)(F)F)cc1</t>
+    <t>UIDXLAWFEKGVOM-QOCYXTBNSA-N</t>
+  </si>
+  <si>
+    <t>[2H]C(=O)/C=C(\c1ccccc1)C1(O)CCC1</t>
   </si>
   <si>
     <t>BRUOEHVDTAORQY-UHFFFAOYSA-N</t>
@@ -1072,16 +1072,10 @@
     <t>COC(=O)CCCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>DQQVADFLIZSTDK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C(=O)OC(C)C)cc1</t>
-  </si>
-  <si>
-    <t>DYPQUENOGZXOGE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccc(Cl)cc1)C(F)(F)F</t>
+    <t>NWVFCQVKCDNHOO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)OC(=O)C(=O)c1ccccc1</t>
   </si>
   <si>
     <t>GCVAEUQDYWOLCF-UHFFFAOYSA-N</t>
@@ -1090,16 +1084,22 @@
     <t>COc1cc(C(C)=O)ccc1OC(C)=O</t>
   </si>
   <si>
-    <t>PIZHFBODNLEQBL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(OCC)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>VUGQIIQFXCXZJU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1cc(C(C)=O)cc(OC)c1OC</t>
+    <t>BVPKHWLMDSKODW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C=C(CCCC)C(=O)C#C[Si](C)(C)C</t>
+  </si>
+  <si>
+    <t>GJFMBFJEVHJVHD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(C)C</t>
+  </si>
+  <si>
+    <t>PJCBRWRFLHBSNH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cc1ccc(C)c(C(=O)c2ccccc2)c1</t>
   </si>
   <si>
     <t>QGGZBXOADPVUPN-UHFFFAOYSA-N</t>
@@ -1108,36 +1108,30 @@
     <t>O=C(CCc1ccccc1)c1ccccc1</t>
   </si>
   <si>
-    <t>PJCBRWRFLHBSNH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C)c(C(=O)c2ccccc2)c1</t>
-  </si>
-  <si>
     <t>OQHGRUHRHLFMBX-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCCC(=O)C(F)(F)F</t>
   </si>
   <si>
+    <t>XPXCYSSTNURNAE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C#CC(=O)OCC</t>
+  </si>
+  <si>
+    <t>CSUUDNFYSFENAE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccccc1C(=O)c1ccccc1</t>
+  </si>
+  <si>
     <t>KPBCVVSDGJBODL-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)c1ccccc1Oc1ccccc1</t>
   </si>
   <si>
-    <t>CSUUDNFYSFENAE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccccc1C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>SWFHGTMLYIBPPA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(=O)c2ccccc2)cc1</t>
-  </si>
-  <si>
     <t>PFIKCDNZZJYSMK-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1150,52 +1144,46 @@
     <t>CCCCCCC(=O)C#Cc1ccccc1</t>
   </si>
   <si>
+    <t>WBMUEFOEEVGDNQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cccc(F)c1Br</t>
+  </si>
+  <si>
     <t>VMHYWKBKHMYRNF-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(c1ccccc1)c1ccccc1Cl</t>
   </si>
   <si>
-    <t>UGVRJVHOJNYEHR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccc(Cl)cc1</t>
-  </si>
-  <si>
     <t>LFBKBXCVHMMYSM-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(CCc1ccccc1)C1CCCCC1</t>
   </si>
   <si>
-    <t>DTEIFMBOVCPJGY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1cccc(Cl)c1)c1ccccn1</t>
-  </si>
-  <si>
-    <t>MDGKXQYPOIIMHW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1cccnc1)c1cccc(Cl)c1</t>
-  </si>
-  <si>
     <t>MLXBLQUBVDCARQ-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>COc1c(Cl)cc(Cl)cc1C(C)=O</t>
   </si>
   <si>
+    <t>QTUYJWKFWYJIOM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(=O)c1ccccc1C(=O)OC</t>
+  </si>
+  <si>
     <t>XBYIXIAOQPIYHO-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCOC(=O)CCCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>QTUYJWKFWYJIOM-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(=O)c1ccccc1C(=O)OC</t>
+    <t>OAMHTTBNEJBIKA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(Cl)(Cl)Cl</t>
   </si>
   <si>
     <t>VYWPPRLJNVHPEU-UHFFFAOYSA-N</t>
@@ -1204,10 +1192,10 @@
     <t>O=C(CCl)c1ccc(Cl)cc1Cl</t>
   </si>
   <si>
-    <t>OAMHTTBNEJBIKA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(Cl)(Cl)Cl</t>
+    <t>JBXKQPGXNRAUQL-HJWRWDBZSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC/C=C\C(=O)C#CC(=O)OCC</t>
   </si>
   <si>
     <t>XVKCCRCIQKVMPK-UHFFFAOYSA-N</t>
@@ -1216,24 +1204,30 @@
     <t>CCCCCCCCC#CC(=O)C(C)(C)C</t>
   </si>
   <si>
+    <t>LJANCPRIUMHGJE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>N#Cc1ccc(C(=O)CBr)cc1</t>
+  </si>
+  <si>
     <t>VUBUXALTYMBEQO-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(c1ccccc1)C(F)(F)C(F)(F)F</t>
   </si>
   <si>
+    <t>JWQLBVFFLIHXHA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccc2ccccc2c1)C(F)(F)F</t>
+  </si>
+  <si>
     <t>VQCWOGKZDGCRES-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(c1cccc2ccccc12)C(F)(F)F</t>
   </si>
   <si>
-    <t>JWQLBVFFLIHXHA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccc2ccccc2c1)C(F)(F)F</t>
-  </si>
-  <si>
     <t>PFJFIFJKDPIALO-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1246,12 +1240,6 @@
     <t>CCCCC#CC(=O)C(F)(F)C(F)(F)F</t>
   </si>
   <si>
-    <t>YNXGVXBSQAEVTO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(OC)c2c1C=C(C(C)=O)CC2</t>
-  </si>
-  <si>
     <t>QQXJNLYVPPBERR-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1264,6 +1252,12 @@
     <t>O=C1CCCC1(c1ccccc1)c1ccccc1</t>
   </si>
   <si>
+    <t>VKYIEQCHVMUBFP-HJWRWDBZSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC/C=C\CC(=O)C#CC(=O)OCC</t>
+  </si>
+  <si>
     <t>LUWXCCCGOWDRJL-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1276,12 +1270,6 @@
     <t>CC(C)(C)c1ccc(C(=O)c2ccccc2)cc1</t>
   </si>
   <si>
-    <t>MIJZKZQWQXKSPA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CNC(=O)c1ccccc1)c1ccccc1</t>
-  </si>
-  <si>
     <t>NQSMEZJWJJVYOI-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1312,6 +1300,12 @@
     <t>CCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
+    <t>YHXHHGDUANVQHE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CBr)c1ccc2ccccc2c1</t>
+  </si>
+  <si>
     <t>VCARCPYEXCPAJO-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1324,30 +1318,12 @@
     <t>C=CCC(C)(C)C(=O)C#CCCCCCCCC</t>
   </si>
   <si>
-    <t>WFKSNAFHIMNMLV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CN(CC(=O)c1ccccc1)C(=O)OC(C)(C)C</t>
-  </si>
-  <si>
-    <t>OHTYZZYAMUVKQS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccc(C(F)(F)F)cc1</t>
-  </si>
-  <si>
     <t>QRJXIADOTSHIRY-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCCC#CC(=O)C(C)(C)CCC</t>
   </si>
   <si>
-    <t>IHGSAQHSAGRWNI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccc(Br)cc1)C(F)(F)F</t>
-  </si>
-  <si>
     <t>RUENABICCRWAEK-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1360,22 +1336,10 @@
     <t>C=C(OC(=O)OCC)C1=C(C)C(=O)CCC1(C)C</t>
   </si>
   <si>
-    <t>KXARYBXYBGQZCM-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CN(CC(=O)c1ccccc1)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>MHLYNSLYUWMONA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C(F)(F)F)cc1C(F)(F)F</t>
-  </si>
-  <si>
-    <t>ABEVIHIQUUXDMS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccccc1Br</t>
+    <t>JRRVWRYHGRGVML-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)CCC(=O)OC</t>
   </si>
   <si>
     <t>ZAVHZGXNVXPEQL-UHFFFAOYSA-N</t>
@@ -1390,30 +1354,12 @@
     <t>CCCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>MYLYBCZMJRPTEU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccn1S(=O)(=O)c1ccc(C)cc1</t>
-  </si>
-  <si>
     <t>MMUXSGDQWCOFKS-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCCC#CC(=O)C(C)(CC)CCC</t>
   </si>
   <si>
-    <t>FCHBFQQIEMUQIF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccnc2cc(Cl)ccc12</t>
-  </si>
-  <si>
-    <t>PGNXIGKGMHOQCA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C(=O)c2ccccc2Br)cc1</t>
-  </si>
-  <si>
     <t>UKYZDGAVBNKBPQ-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1432,6 +1378,12 @@
     <t>CCCCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
+    <t>FKJSFKCZZIXQIP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CBr)c1ccc(Br)cc1</t>
+  </si>
+  <si>
     <t>LQWPEACAJAMZQF-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1456,16 +1408,10 @@
     <t>CCCCCCCCC#CC(=O)C(CC)(CC)CCC</t>
   </si>
   <si>
-    <t>YAPSCCPUKNXEOX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccccc1C(=O)c1ccnc2cc(Cl)ccc12</t>
-  </si>
-  <si>
-    <t>ZKMWWSYZEDDBGZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(C(=O)c2ccnc3cc(Cl)ccc23)cc1</t>
+    <t>PDRBPSUHUITJJU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C[Si](C)(C)C#CC(=O)c1ccccc1Br</t>
   </si>
   <si>
     <t>HJPJVTHMENRJQA-UHFFFAOYSA-N</t>
@@ -1516,12 +1462,24 @@
     <t>CC(C)(C)OC(=O)CN1CCC2(CC1)C(=O)Cc1ccccc12</t>
   </si>
   <si>
+    <t>ZCAPJTBGWAUMSA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[Si](C)(C)OCCC(=O)C#CCCCC1OCCO1</t>
+  </si>
+  <si>
     <t>VUXIOSYYRVXOOT-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
+    <t>OVXHPUNWJSQAEN-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[Si](C)(C)Oc1ccccc1C(=O)C#C[Si](C)(C)C</t>
+  </si>
+  <si>
     <t>JGUYBMKIKPABSY-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1540,10 +1498,16 @@
     <t>CCCCCCCCCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
-    <t>QTGQNPULXWGQBL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCCN1CCN(C2=NCC(F)C=N2)CC1)c1ccc(F)cc1</t>
+    <t>XVGXRUMLDHHLAO-QFDGZYDSSA-N</t>
+  </si>
+  <si>
+    <t>CC#CC(=O)[C@@H](C)[C@H]1CC[C@H]2[C@H]3CC=C4CCCC[C@]4(C)[C@H]3CC[C@]12C</t>
+  </si>
+  <si>
+    <t>SZZNLQONRHATKI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(=O)C#C[Si](C)(C)C)c1O[Si](C)(C)C(C)(C)C</t>
   </si>
   <si>
     <t>AJJMCZDTONCKDU-UHFFFAOYSA-N</t>
@@ -1552,6 +1516,12 @@
     <t>Cc1ccc(S(=O)(=O)NCc2ccccc2C(=O)c2ccccc2)cc1</t>
   </si>
   <si>
+    <t>SGKHGSBZEDQNJO-YQMVHVRGSA-N</t>
+  </si>
+  <si>
+    <t>CC#CC(=O)C[C@@H](C)[C@H]1CC[C@H]2[C@H]3CC=C4CCCC[C@]4(C)[C@H]3CC[C@]12C</t>
+  </si>
+  <si>
     <t>PVSHPLKPKFIRHX-UHFFFAOYSA-N</t>
   </si>
   <si>
@@ -1562,12 +1532,6 @@
   </si>
   <si>
     <t>COc1c(C)c2c(c([Si](C)(C)C(C)(C)C)c1CC(=O)C1=CCCC1)C(=O)OC2</t>
-  </si>
-  <si>
-    <t>BLNSEHDIFVBBKV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(CCN(CC(=O)c2ccc(OCc3ccccc3)cc2)C(=O)c2ccccc2)cc1OC</t>
   </si>
 </sst>
 </file>
@@ -11145,234 +11109,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1828800" y="316896750"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>252</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>252</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="253" name="Picture 252" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId252"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="318163575"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>253</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>253</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="254" name="Picture 253" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId253"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="319430400"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>254</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>254</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="255" name="Picture 254" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId254"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="320697225"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>255</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>255</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="256" name="Picture 255" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId255"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="321964050"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>256</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>256</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="257" name="Picture 256" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId256"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="323230875"/>
-          <a:ext cx="952500" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>257</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>257</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="258" name="Picture 257" descr="f"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId257"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="324497700"/>
           <a:ext cx="952500" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11670,7 +11406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D258"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="17.42578125" customWidth="1"/>
@@ -11709,7 +11445,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>72.057514876</v>
+        <v>70.041864812</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="100" customHeight="1">
@@ -11720,7 +11456,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>76.032443</v>
+        <v>72.057514876</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="100" customHeight="1">
@@ -11731,7 +11467,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>82.041864812</v>
+        <v>73.063791622</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="100" customHeight="1">
@@ -11742,7 +11478,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>84.057514876</v>
+        <v>76.032443</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="100" customHeight="1">
@@ -11753,7 +11489,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>86.07316494</v>
+        <v>82.041864812</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="100" customHeight="1">
@@ -11764,7 +11500,7 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>92.00289246</v>
+        <v>84.057514876</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="100" customHeight="1">
@@ -11775,7 +11511,7 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>94.023021188</v>
+        <v>84.057514876</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="100" customHeight="1">
@@ -11786,7 +11522,7 @@
         <v>21</v>
       </c>
       <c r="C10">
-        <v>96.057514876</v>
+        <v>86.07316494</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="100" customHeight="1">
@@ -11797,7 +11533,7 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>98.07316494</v>
+        <v>92.00289246</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="100" customHeight="1">
@@ -11808,7 +11544,7 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>98.07316494</v>
+        <v>94.023021188</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="100" customHeight="1">
@@ -11819,7 +11555,7 @@
         <v>27</v>
       </c>
       <c r="C13">
-        <v>100.088815004</v>
+        <v>96.057514876</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="100" customHeight="1">
@@ -11830,7 +11566,7 @@
         <v>29</v>
       </c>
       <c r="C14">
-        <v>100.088815004</v>
+        <v>96.057514876</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="100" customHeight="1">
@@ -11841,7 +11577,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>101.084063972</v>
+        <v>98.07316494</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="100" customHeight="1">
@@ -11852,7 +11588,7 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>110.036779432</v>
+        <v>100.088815004</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="100" customHeight="1">
@@ -11863,7 +11599,7 @@
         <v>35</v>
       </c>
       <c r="C17">
-        <v>110.07316494</v>
+        <v>100.088815004</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="100" customHeight="1">
@@ -11874,7 +11610,7 @@
         <v>37</v>
       </c>
       <c r="C18">
-        <v>111.068413908</v>
+        <v>101.09509175</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="100" customHeight="1">
@@ -11885,7 +11621,7 @@
         <v>39</v>
       </c>
       <c r="C19">
-        <v>112.013599376</v>
+        <v>102.031694052</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="100" customHeight="1">
@@ -11896,7 +11632,7 @@
         <v>41</v>
       </c>
       <c r="C20">
-        <v>112.088815004</v>
+        <v>107.048141558</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="100" customHeight="1">
@@ -11907,7 +11643,7 @@
         <v>43</v>
       </c>
       <c r="C21">
-        <v>112.088815004</v>
+        <v>110.07316494</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="100" customHeight="1">
@@ -11918,7 +11654,7 @@
         <v>45</v>
       </c>
       <c r="C22">
-        <v>116.047344116</v>
+        <v>110.07316494</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="100" customHeight="1">
@@ -11929,7 +11665,7 @@
         <v>47</v>
       </c>
       <c r="C23">
-        <v>118.06299418</v>
+        <v>110.07316494</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="100" customHeight="1">
@@ -11940,7 +11676,7 @@
         <v>49</v>
       </c>
       <c r="C24">
-        <v>120.057514876</v>
+        <v>111.068413908</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="100" customHeight="1">
@@ -11951,7 +11687,7 @@
         <v>51</v>
       </c>
       <c r="C25">
-        <v>121.052763844</v>
+        <v>112.013599376</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="100" customHeight="1">
@@ -11962,7 +11698,7 @@
         <v>53</v>
       </c>
       <c r="C26">
-        <v>121.052763844</v>
+        <v>112.088815004</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="100" customHeight="1">
@@ -11973,7 +11709,7 @@
         <v>55</v>
       </c>
       <c r="C27">
-        <v>121.052763844</v>
+        <v>112.088815004</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="100" customHeight="1">
@@ -11984,7 +11720,7 @@
         <v>57</v>
       </c>
       <c r="C28">
-        <v>124.088815004</v>
+        <v>112.088815004</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="100" customHeight="1">
@@ -11995,7 +11731,7 @@
         <v>59</v>
       </c>
       <c r="C29">
-        <v>124.088815004</v>
+        <v>112.088815004</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="100" customHeight="1">
@@ -12006,7 +11742,7 @@
         <v>61</v>
       </c>
       <c r="C30">
-        <v>125.963920108</v>
+        <v>116.047344116</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="100" customHeight="1">
@@ -12017,7 +11753,7 @@
         <v>63</v>
       </c>
       <c r="C31">
-        <v>126.013935812</v>
+        <v>120.057514876</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="100" customHeight="1">
@@ -12028,7 +11764,7 @@
         <v>65</v>
       </c>
       <c r="C32">
-        <v>126.013935812</v>
+        <v>121.052763844</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="100" customHeight="1">
@@ -12039,7 +11775,7 @@
         <v>67</v>
       </c>
       <c r="C33">
-        <v>126.104465068</v>
+        <v>124.088815004</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="100" customHeight="1">
@@ -12050,7 +11786,7 @@
         <v>69</v>
       </c>
       <c r="C34">
-        <v>126.104465068</v>
+        <v>124.088815004</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="100" customHeight="1">
@@ -12061,7 +11797,7 @@
         <v>71</v>
       </c>
       <c r="C35">
-        <v>126.104465068</v>
+        <v>124.088815004</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="100" customHeight="1">
@@ -12072,7 +11808,7 @@
         <v>73</v>
       </c>
       <c r="C36">
-        <v>127.00918478</v>
+        <v>125.963920108</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="100" customHeight="1">
@@ -12083,7 +11819,7 @@
         <v>75</v>
       </c>
       <c r="C37">
-        <v>128.120115132</v>
+        <v>126.013935812</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="100" customHeight="1">
@@ -12094,7 +11830,7 @@
         <v>77</v>
       </c>
       <c r="C38">
-        <v>132.057514876</v>
+        <v>126.104465068</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="100" customHeight="1">
@@ -12105,7 +11841,7 @@
         <v>79</v>
       </c>
       <c r="C39">
-        <v>134.07316494</v>
+        <v>126.104465068</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="100" customHeight="1">
@@ -12116,7 +11852,7 @@
         <v>81</v>
       </c>
       <c r="C40">
-        <v>134.07316494</v>
+        <v>128.120115132</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="100" customHeight="1">
@@ -12127,7 +11863,7 @@
         <v>83</v>
       </c>
       <c r="C41">
-        <v>134.07316494</v>
+        <v>130.06299418</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="100" customHeight="1">
@@ -12138,7 +11874,7 @@
         <v>85</v>
       </c>
       <c r="C42">
-        <v>134.07316494</v>
+        <v>130.06299418</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="100" customHeight="1">
@@ -12149,7 +11885,7 @@
         <v>87</v>
       </c>
       <c r="C43">
-        <v>134.07316494</v>
+        <v>130.06299418</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="100" customHeight="1">
@@ -12160,7 +11896,7 @@
         <v>89</v>
       </c>
       <c r="C44">
-        <v>135.068413908</v>
+        <v>132.057514876</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="100" customHeight="1">
@@ -12171,7 +11907,7 @@
         <v>91</v>
       </c>
       <c r="C45">
-        <v>136.088815004</v>
+        <v>133.063791622</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="100" customHeight="1">
@@ -12182,7 +11918,7 @@
         <v>93</v>
       </c>
       <c r="C46">
-        <v>138.048093064</v>
+        <v>134.07316494</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="100" customHeight="1">
@@ -12193,7 +11929,7 @@
         <v>95</v>
       </c>
       <c r="C47">
-        <v>138.048093064</v>
+        <v>134.07316494</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="100" customHeight="1">
@@ -12204,7 +11940,7 @@
         <v>97</v>
       </c>
       <c r="C48">
-        <v>138.048093064</v>
+        <v>134.07316494</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="100" customHeight="1">
@@ -12215,7 +11951,7 @@
         <v>99</v>
       </c>
       <c r="C49">
-        <v>138.048093064</v>
+        <v>134.07316494</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="100" customHeight="1">
@@ -12226,7 +11962,7 @@
         <v>101</v>
       </c>
       <c r="C50">
-        <v>138.104465068</v>
+        <v>135.068413908</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="100" customHeight="1">
@@ -12237,7 +11973,7 @@
         <v>103</v>
       </c>
       <c r="C51">
-        <v>138.104465068</v>
+        <v>136.088815004</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="100" customHeight="1">
@@ -12248,7 +11984,7 @@
         <v>105</v>
       </c>
       <c r="C52">
-        <v>138.104465068</v>
+        <v>137.058706242</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="100" customHeight="1">
@@ -12259,7 +11995,7 @@
         <v>107</v>
       </c>
       <c r="C53">
-        <v>140.120115132</v>
+        <v>138.048093064</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="100" customHeight="1">
@@ -12270,7 +12006,7 @@
         <v>109</v>
       </c>
       <c r="C54">
-        <v>140.120115132</v>
+        <v>138.048093064</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="100" customHeight="1">
@@ -12281,7 +12017,7 @@
         <v>111</v>
       </c>
       <c r="C55">
-        <v>142.079393192</v>
+        <v>138.104465068</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="100" customHeight="1">
@@ -12292,7 +12028,7 @@
         <v>113</v>
       </c>
       <c r="C56">
-        <v>144.057514876</v>
+        <v>138.104465068</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="100" customHeight="1">
@@ -12303,7 +12039,7 @@
         <v>115</v>
       </c>
       <c r="C57">
-        <v>144.078644244</v>
+        <v>140.047344116</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="100" customHeight="1">
@@ -12314,7 +12050,7 @@
         <v>117</v>
       </c>
       <c r="C58">
-        <v>144.078644244</v>
+        <v>140.120115132</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="100" customHeight="1">
@@ -12325,7 +12061,7 @@
         <v>119</v>
       </c>
       <c r="C59">
-        <v>145.052763844</v>
+        <v>141.009169206</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="100" customHeight="1">
@@ -12336,7 +12072,7 @@
         <v>121</v>
       </c>
       <c r="C60">
-        <v>146.07316494</v>
+        <v>142.079393192</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="100" customHeight="1">
@@ -12347,7 +12083,7 @@
         <v>123</v>
       </c>
       <c r="C61">
-        <v>146.07316494</v>
+        <v>143.131014164</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="100" customHeight="1">
@@ -12358,7 +12094,7 @@
         <v>125</v>
       </c>
       <c r="C62">
-        <v>146.07316494</v>
+        <v>144.057514876</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="100" customHeight="1">
@@ -12369,7 +12105,7 @@
         <v>127</v>
       </c>
       <c r="C63">
-        <v>148.052429496</v>
+        <v>144.078644244</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="100" customHeight="1">
@@ -12380,7 +12116,7 @@
         <v>129</v>
       </c>
       <c r="C64">
-        <v>148.088815004</v>
+        <v>144.078644244</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="100" customHeight="1">
@@ -12391,7 +12127,7 @@
         <v>131</v>
       </c>
       <c r="C65">
-        <v>148.088815004</v>
+        <v>144.078644244</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="100" customHeight="1">
@@ -12402,7 +12138,7 @@
         <v>133</v>
       </c>
       <c r="C66">
-        <v>148.088815004</v>
+        <v>144.078644244</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="100" customHeight="1">
@@ -12413,7 +12149,7 @@
         <v>135</v>
       </c>
       <c r="C67">
-        <v>148.088815004</v>
+        <v>145.052763844</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="100" customHeight="1">
@@ -12424,7 +12160,7 @@
         <v>137</v>
       </c>
       <c r="C68">
-        <v>149.084063972</v>
+        <v>146.07316494</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="100" customHeight="1">
@@ -12435,7 +12171,7 @@
         <v>139</v>
       </c>
       <c r="C69">
-        <v>150.06807956</v>
+        <v>146.07316494</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="100" customHeight="1">
@@ -12446,7 +12182,7 @@
         <v>141</v>
       </c>
       <c r="C70">
-        <v>150.06807956</v>
+        <v>146.11069332</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="100" customHeight="1">
@@ -12457,7 +12193,7 @@
         <v>143</v>
       </c>
       <c r="C71">
-        <v>150.06807956</v>
+        <v>148.052429496</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="100" customHeight="1">
@@ -12468,7 +12204,7 @@
         <v>145</v>
       </c>
       <c r="C72">
-        <v>150.06807956</v>
+        <v>148.088815004</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="100" customHeight="1">
@@ -12479,7 +12215,7 @@
         <v>147</v>
       </c>
       <c r="C73">
-        <v>150.06807956</v>
+        <v>148.088815004</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="100" customHeight="1">
@@ -12490,7 +12226,7 @@
         <v>149</v>
       </c>
       <c r="C74">
-        <v>150.104465068</v>
+        <v>148.088815004</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="100" customHeight="1">
@@ -12501,7 +12237,7 @@
         <v>151</v>
       </c>
       <c r="C75">
-        <v>151.063328528</v>
+        <v>149.084063972</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="100" customHeight="1">
@@ -12512,7 +12248,7 @@
         <v>153</v>
       </c>
       <c r="C76">
-        <v>152.063743128</v>
+        <v>149.084063972</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="100" customHeight="1">
@@ -12523,7 +12259,7 @@
         <v>155</v>
       </c>
       <c r="C77">
-        <v>152.120115132</v>
+        <v>150.06807956</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="100" customHeight="1">
@@ -12534,7 +12270,7 @@
         <v>157</v>
       </c>
       <c r="C78">
-        <v>154.018542524</v>
+        <v>150.06807956</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="100" customHeight="1">
@@ -12545,7 +12281,7 @@
         <v>159</v>
       </c>
       <c r="C79">
-        <v>154.018542524</v>
+        <v>150.06807956</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="100" customHeight="1">
@@ -12556,7 +12292,7 @@
         <v>161</v>
       </c>
       <c r="C80">
-        <v>154.04523594</v>
+        <v>150.06807956</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="100" customHeight="1">
@@ -12567,7 +12303,7 @@
         <v>163</v>
       </c>
       <c r="C81">
-        <v>154.135765196</v>
+        <v>150.104465068</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="100" customHeight="1">
@@ -12578,7 +12314,7 @@
         <v>165</v>
       </c>
       <c r="C82">
-        <v>156.038671252</v>
+        <v>151.063328528</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="100" customHeight="1">
@@ -12589,7 +12325,7 @@
         <v>167</v>
       </c>
       <c r="C83">
-        <v>156.038671252</v>
+        <v>152.033219766</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="100" customHeight="1">
@@ -12600,7 +12336,7 @@
         <v>169</v>
       </c>
       <c r="C84">
-        <v>156.078644244</v>
+        <v>152.120115132</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="100" customHeight="1">
@@ -12611,7 +12347,7 @@
         <v>171</v>
       </c>
       <c r="C85">
-        <v>158.07316494</v>
+        <v>154.018542524</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="100" customHeight="1">
@@ -12622,7 +12358,7 @@
         <v>173</v>
       </c>
       <c r="C86">
-        <v>158.094294308</v>
+        <v>154.06299418</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="100" customHeight="1">
@@ -12633,7 +12369,7 @@
         <v>175</v>
       </c>
       <c r="C87">
-        <v>159.924947756</v>
+        <v>154.135765196</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="100" customHeight="1">
@@ -12644,7 +12380,7 @@
         <v>177</v>
       </c>
       <c r="C88">
-        <v>159.95237688</v>
+        <v>156.038671252</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="100" customHeight="1">
@@ -12655,7 +12391,7 @@
         <v>179</v>
       </c>
       <c r="C89">
-        <v>160.06997138</v>
+        <v>156.078644244</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="100" customHeight="1">
@@ -12666,7 +12402,7 @@
         <v>181</v>
       </c>
       <c r="C90">
-        <v>160.088815004</v>
+        <v>158.07316494</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="100" customHeight="1">
@@ -12677,7 +12413,7 @@
         <v>183</v>
       </c>
       <c r="C91">
-        <v>162.048093064</v>
+        <v>158.094294308</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="100" customHeight="1">
@@ -12688,7 +12424,7 @@
         <v>185</v>
       </c>
       <c r="C92">
-        <v>162.104465068</v>
+        <v>158.094294308</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="100" customHeight="1">
@@ -12699,7 +12435,7 @@
         <v>187</v>
       </c>
       <c r="C93">
-        <v>162.104465068</v>
+        <v>158.094294308</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="100" customHeight="1">
@@ -12710,7 +12446,7 @@
         <v>189</v>
       </c>
       <c r="C94">
-        <v>163.099714036</v>
+        <v>159.924947756</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="100" customHeight="1">
@@ -12721,7 +12457,7 @@
         <v>191</v>
       </c>
       <c r="C95">
-        <v>163.099714036</v>
+        <v>159.95237688</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="100" customHeight="1">
@@ -12732,7 +12468,7 @@
         <v>193</v>
       </c>
       <c r="C96">
-        <v>164.029585876</v>
+        <v>160.06997138</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="100" customHeight="1">
@@ -12743,7 +12479,7 @@
         <v>195</v>
       </c>
       <c r="C97">
-        <v>164.047344116</v>
+        <v>160.088815004</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="100" customHeight="1">
@@ -12754,7 +12490,7 @@
         <v>197</v>
       </c>
       <c r="C98">
-        <v>164.083729624</v>
+        <v>162.048093064</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="100" customHeight="1">
@@ -12765,7 +12501,7 @@
         <v>199</v>
       </c>
       <c r="C99">
-        <v>164.083729624</v>
+        <v>162.104465068</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="100" customHeight="1">
@@ -12776,7 +12512,7 @@
         <v>201</v>
       </c>
       <c r="C100">
-        <v>164.120115132</v>
+        <v>162.104465068</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="100" customHeight="1">
@@ -12787,7 +12523,7 @@
         <v>203</v>
       </c>
       <c r="C101">
-        <v>165.042593084</v>
+        <v>163.983677008</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="100" customHeight="1">
@@ -12798,7 +12534,7 @@
         <v>205</v>
       </c>
       <c r="C102">
-        <v>165.078978592</v>
+        <v>164.029585876</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="100" customHeight="1">
@@ -12809,7 +12545,7 @@
         <v>207</v>
       </c>
       <c r="C103">
-        <v>166.099379688</v>
+        <v>164.047344116</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="100" customHeight="1">
@@ -12820,7 +12556,7 @@
         <v>209</v>
       </c>
       <c r="C104">
-        <v>168.034192588</v>
+        <v>164.083729624</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="100" customHeight="1">
@@ -12831,7 +12567,7 @@
         <v>211</v>
       </c>
       <c r="C105">
-        <v>168.034192588</v>
+        <v>164.101271508</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="100" customHeight="1">
@@ -12842,7 +12578,7 @@
         <v>213</v>
       </c>
       <c r="C106">
-        <v>168.034192588</v>
+        <v>164.120115132</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="100" customHeight="1">
@@ -12853,7 +12589,7 @@
         <v>215</v>
       </c>
       <c r="C107">
-        <v>168.058657748</v>
+        <v>165.078978592</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="100" customHeight="1">
@@ -12864,7 +12600,7 @@
         <v>217</v>
       </c>
       <c r="C108">
-        <v>168.15141526</v>
+        <v>168.034192588</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="100" customHeight="1">
@@ -12875,7 +12611,7 @@
         <v>219</v>
       </c>
       <c r="C109">
-        <v>170.07316494</v>
+        <v>168.034192588</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="100" customHeight="1">
@@ -12886,7 +12622,7 @@
         <v>221</v>
       </c>
       <c r="C110">
-        <v>170.094294308</v>
+        <v>168.058657748</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="100" customHeight="1">
@@ -12897,7 +12633,7 @@
         <v>223</v>
       </c>
       <c r="C111">
-        <v>172.088815004</v>
+        <v>168.15141526</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="100" customHeight="1">
@@ -12908,7 +12644,7 @@
         <v>225</v>
       </c>
       <c r="C112">
-        <v>172.088815004</v>
+        <v>169.029441556</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="100" customHeight="1">
@@ -12919,7 +12655,7 @@
         <v>227</v>
       </c>
       <c r="C113">
-        <v>172.088815004</v>
+        <v>170.07316494</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="100" customHeight="1">
@@ -12930,7 +12666,7 @@
         <v>229</v>
       </c>
       <c r="C114">
-        <v>173.968026944</v>
+        <v>170.094294308</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="100" customHeight="1">
@@ -12941,7 +12677,7 @@
         <v>231</v>
       </c>
       <c r="C115">
-        <v>174.02924944</v>
+        <v>172.088815004</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="100" customHeight="1">
@@ -12952,7 +12688,7 @@
         <v>233</v>
       </c>
       <c r="C116">
-        <v>174.104465068</v>
+        <v>172.088815004</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="100" customHeight="1">
@@ -12963,7 +12699,7 @@
         <v>235</v>
       </c>
       <c r="C117">
-        <v>176.120115132</v>
+        <v>172.088815004</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="100" customHeight="1">
@@ -12974,7 +12710,7 @@
         <v>237</v>
       </c>
       <c r="C118">
-        <v>176.120115132</v>
+        <v>172.088815004</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="100" customHeight="1">
@@ -12985,7 +12721,7 @@
         <v>239</v>
       </c>
       <c r="C119">
-        <v>177.078978592</v>
+        <v>172.109944372</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="100" customHeight="1">
@@ -12996,7 +12732,7 @@
         <v>241</v>
       </c>
       <c r="C120">
-        <v>177.1153641</v>
+        <v>173.968026944</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="100" customHeight="1">
@@ -13007,7 +12743,7 @@
         <v>243</v>
       </c>
       <c r="C121">
-        <v>178.060549568</v>
+        <v>174.02924944</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="100" customHeight="1">
@@ -13018,7 +12754,7 @@
         <v>245</v>
       </c>
       <c r="C122">
-        <v>178.06299418</v>
+        <v>176.029585876</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="100" customHeight="1">
@@ -13029,7 +12765,7 @@
         <v>247</v>
       </c>
       <c r="C123">
-        <v>178.06299418</v>
+        <v>176.029585876</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="100" customHeight="1">
@@ -13040,7 +12776,7 @@
         <v>249</v>
       </c>
       <c r="C124">
-        <v>178.135765196</v>
+        <v>176.120115132</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="100" customHeight="1">
@@ -13051,7 +12787,7 @@
         <v>251</v>
       </c>
       <c r="C125">
-        <v>179.058243148</v>
+        <v>178.043007684</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="100" customHeight="1">
@@ -13062,7 +12798,7 @@
         <v>253</v>
       </c>
       <c r="C126">
-        <v>180.038671252</v>
+        <v>178.060549568</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="100" customHeight="1">
@@ -13073,7 +12809,7 @@
         <v>255</v>
       </c>
       <c r="C127">
-        <v>180.076199632</v>
+        <v>178.06299418</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="100" customHeight="1">
@@ -13084,7 +12820,7 @@
         <v>257</v>
       </c>
       <c r="C128">
-        <v>180.078644244</v>
+        <v>178.06299418</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="100" customHeight="1">
@@ -13095,7 +12831,7 @@
         <v>259</v>
       </c>
       <c r="C129">
-        <v>180.078644244</v>
+        <v>178.099379688</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="100" customHeight="1">
@@ -13106,7 +12842,7 @@
         <v>261</v>
       </c>
       <c r="C130">
-        <v>180.078644244</v>
+        <v>178.135765196</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="100" customHeight="1">
@@ -13117,7 +12853,7 @@
         <v>263</v>
       </c>
       <c r="C131">
-        <v>180.078644244</v>
+        <v>179.058243148</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="100" customHeight="1">
@@ -13128,7 +12864,7 @@
         <v>265</v>
       </c>
       <c r="C132">
-        <v>183.068413908</v>
+        <v>180.038671252</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="100" customHeight="1">
@@ -13139,7 +12875,7 @@
         <v>267</v>
       </c>
       <c r="C133">
-        <v>183.068413908</v>
+        <v>180.076199632</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="100" customHeight="1">
@@ -13150,7 +12886,7 @@
         <v>269</v>
       </c>
       <c r="C134">
-        <v>183.068413908</v>
+        <v>180.078644244</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="100" customHeight="1">
@@ -13161,7 +12897,7 @@
         <v>271</v>
       </c>
       <c r="C135">
-        <v>184.029107208</v>
+        <v>180.078644244</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="100" customHeight="1">
@@ -13172,7 +12908,7 @@
         <v>273</v>
       </c>
       <c r="C136">
-        <v>185.0874351</v>
+        <v>180.078644244</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="100" customHeight="1">
@@ -13183,7 +12919,7 @@
         <v>275</v>
       </c>
       <c r="C137">
-        <v>186.104465068</v>
+        <v>180.078644244</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="100" customHeight="1">
@@ -13194,7 +12930,7 @@
         <v>277</v>
       </c>
       <c r="C138">
-        <v>186.104465068</v>
+        <v>180.15141526</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="100" customHeight="1">
@@ -13205,7 +12941,7 @@
         <v>279</v>
       </c>
       <c r="C139">
-        <v>187.979570172</v>
+        <v>180.15141526</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="100" customHeight="1">
@@ -13216,7 +12952,7 @@
         <v>281</v>
       </c>
       <c r="C140">
-        <v>187.979570172</v>
+        <v>182.091849696</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="100" customHeight="1">
@@ -13227,7 +12963,7 @@
         <v>283</v>
       </c>
       <c r="C141">
-        <v>187.983677008</v>
+        <v>184.029107208</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="100" customHeight="1">
@@ -13238,7 +12974,7 @@
         <v>285</v>
       </c>
       <c r="C142">
-        <v>188.044899504</v>
+        <v>186.104465068</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="100" customHeight="1">
@@ -13249,7 +12985,7 @@
         <v>287</v>
       </c>
       <c r="C143">
-        <v>188.044899504</v>
+        <v>186.104465068</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="100" customHeight="1">
@@ -13260,7 +12996,7 @@
         <v>289</v>
       </c>
       <c r="C144">
-        <v>188.044899504</v>
+        <v>186.104465068</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="100" customHeight="1">
@@ -13271,7 +13007,7 @@
         <v>291</v>
       </c>
       <c r="C145">
-        <v>188.120115132</v>
+        <v>186.125594436</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="100" customHeight="1">
@@ -13282,7 +13018,7 @@
         <v>293</v>
       </c>
       <c r="C146">
-        <v>189.924111444</v>
+        <v>187.979570172</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="100" customHeight="1">
@@ -13293,7 +13029,7 @@
         <v>295</v>
       </c>
       <c r="C147">
-        <v>190.135765196</v>
+        <v>187.983677008</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="100" customHeight="1">
@@ -13304,7 +13040,7 @@
         <v>297</v>
       </c>
       <c r="C148">
-        <v>191.094628656</v>
+        <v>188.120115132</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="100" customHeight="1">
@@ -13315,7 +13051,7 @@
         <v>299</v>
       </c>
       <c r="C149">
-        <v>192.078644244</v>
+        <v>189.924111444</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="100" customHeight="1">
@@ -13326,7 +13062,7 @@
         <v>301</v>
       </c>
       <c r="C150">
-        <v>192.078644244</v>
+        <v>190.135765196</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="100" customHeight="1">
@@ -13337,7 +13073,7 @@
         <v>303</v>
       </c>
       <c r="C151">
-        <v>192.15141526</v>
+        <v>192.078644244</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="100" customHeight="1">
@@ -13348,7 +13084,7 @@
         <v>305</v>
       </c>
       <c r="C152">
-        <v>192.15141526</v>
+        <v>192.078644244</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="100" customHeight="1">
@@ -13359,7 +13095,7 @@
         <v>307</v>
       </c>
       <c r="C153">
-        <v>194.094294308</v>
+        <v>192.078644244</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="100" customHeight="1">
@@ -13370,7 +13106,7 @@
         <v>309</v>
       </c>
       <c r="C154">
-        <v>194.167065324</v>
+        <v>192.15141526</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="100" customHeight="1">
@@ -13381,7 +13117,7 @@
         <v>311</v>
       </c>
       <c r="C155">
-        <v>196.088815004</v>
+        <v>192.15141526</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="100" customHeight="1">
@@ -13392,7 +13128,7 @@
         <v>313</v>
       </c>
       <c r="C156">
-        <v>196.088815004</v>
+        <v>194.094294308</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="100" customHeight="1">
@@ -13403,7 +13139,7 @@
         <v>315</v>
       </c>
       <c r="C157">
-        <v>196.088815004</v>
+        <v>194.167065324</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="100" customHeight="1">
@@ -13425,7 +13161,7 @@
         <v>319</v>
       </c>
       <c r="C159">
-        <v>196.10749976</v>
+        <v>196.088815004</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="100" customHeight="1">
@@ -13436,7 +13172,7 @@
         <v>321</v>
       </c>
       <c r="C160">
-        <v>197.084063972</v>
+        <v>196.10749976</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="100" customHeight="1">
@@ -13447,7 +13183,7 @@
         <v>323</v>
       </c>
       <c r="C161">
-        <v>197.084063972</v>
+        <v>197.968026944</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="100" customHeight="1">
@@ -13458,7 +13194,7 @@
         <v>325</v>
       </c>
       <c r="C162">
-        <v>197.084063972</v>
+        <v>197.968026944</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="100" customHeight="1">
@@ -13491,7 +13227,7 @@
         <v>331</v>
       </c>
       <c r="C165">
-        <v>197.968026944</v>
+        <v>198.02924944</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="100" customHeight="1">
@@ -13502,7 +13238,7 @@
         <v>333</v>
       </c>
       <c r="C166">
-        <v>197.968026944</v>
+        <v>198.198365452</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="100" customHeight="1">
@@ -13513,7 +13249,7 @@
         <v>335</v>
       </c>
       <c r="C167">
-        <v>198.02924944</v>
+        <v>200.04042084</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="100" customHeight="1">
@@ -13524,7 +13260,7 @@
         <v>337</v>
       </c>
       <c r="C168">
-        <v>198.198365452</v>
+        <v>200.063743128</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="100" customHeight="1">
@@ -13535,7 +13271,7 @@
         <v>339</v>
       </c>
       <c r="C169">
-        <v>200.04042084</v>
+        <v>200.083729624</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="100" customHeight="1">
@@ -13546,7 +13282,7 @@
         <v>341</v>
       </c>
       <c r="C170">
-        <v>200.063743128</v>
+        <v>202.06299418</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="100" customHeight="1">
@@ -13557,7 +13293,7 @@
         <v>343</v>
       </c>
       <c r="C171">
-        <v>200.083729624</v>
+        <v>202.099379688</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="100" customHeight="1">
@@ -13579,7 +13315,7 @@
         <v>347</v>
       </c>
       <c r="C173">
-        <v>204.039814124</v>
+        <v>203.105656434</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="100" customHeight="1">
@@ -13623,7 +13359,7 @@
         <v>355</v>
       </c>
       <c r="C177">
-        <v>207.990277088</v>
+        <v>208.073558864</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="100" customHeight="1">
@@ -13634,7 +13370,7 @@
         <v>357</v>
       </c>
       <c r="C178">
-        <v>208.073558864</v>
+        <v>208.12834179</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="100" customHeight="1">
@@ -13645,7 +13381,7 @@
         <v>359</v>
       </c>
       <c r="C179">
-        <v>208.109944372</v>
+        <v>208.182715388</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="100" customHeight="1">
@@ -13656,7 +13392,7 @@
         <v>361</v>
       </c>
       <c r="C180">
-        <v>210.089208928</v>
+        <v>210.104465068</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="100" customHeight="1">
@@ -13678,7 +13414,7 @@
         <v>365</v>
       </c>
       <c r="C182">
-        <v>210.104465068</v>
+        <v>210.123149824</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="100" customHeight="1">
@@ -13689,7 +13425,7 @@
         <v>367</v>
       </c>
       <c r="C183">
-        <v>210.123149824</v>
+        <v>210.125594436</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="100" customHeight="1">
@@ -13722,7 +13458,7 @@
         <v>373</v>
       </c>
       <c r="C186">
-        <v>212.083729624</v>
+        <v>212.120115132</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="100" customHeight="1">
@@ -13733,7 +13469,7 @@
         <v>375</v>
       </c>
       <c r="C187">
-        <v>212.120115132</v>
+        <v>214.135765196</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="100" customHeight="1">
@@ -13744,7 +13480,7 @@
         <v>377</v>
       </c>
       <c r="C188">
-        <v>214.135765196</v>
+        <v>215.958605132</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="100" customHeight="1">
@@ -13766,7 +13502,7 @@
         <v>381</v>
       </c>
       <c r="C190">
-        <v>216.034192588</v>
+        <v>216.15141526</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="100" customHeight="1">
@@ -13777,7 +13513,7 @@
         <v>383</v>
       </c>
       <c r="C191">
-        <v>216.15141526</v>
+        <v>217.990134856</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="100" customHeight="1">
@@ -13788,7 +13524,7 @@
         <v>385</v>
       </c>
       <c r="C192">
-        <v>217.029441556</v>
+        <v>220.109944372</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="100" customHeight="1">
@@ -13799,7 +13535,7 @@
         <v>387</v>
       </c>
       <c r="C193">
-        <v>217.029441556</v>
+        <v>220.109944372</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="100" customHeight="1">
@@ -13810,7 +13546,7 @@
         <v>389</v>
       </c>
       <c r="C194">
-        <v>217.990134856</v>
+        <v>221.94059782</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="100" customHeight="1">
@@ -13821,7 +13557,7 @@
         <v>391</v>
       </c>
       <c r="C195">
-        <v>220.109944372</v>
+        <v>221.94059782</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="100" customHeight="1">
@@ -13832,7 +13568,7 @@
         <v>393</v>
       </c>
       <c r="C196">
-        <v>220.109944372</v>
+        <v>222.125594436</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="100" customHeight="1">
@@ -13843,7 +13579,7 @@
         <v>395</v>
       </c>
       <c r="C197">
-        <v>221.94059782</v>
+        <v>222.198365452</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="100" customHeight="1">
@@ -13854,7 +13590,7 @@
         <v>397</v>
       </c>
       <c r="C198">
-        <v>221.94059782</v>
+        <v>222.963275912</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="100" customHeight="1">
@@ -13865,7 +13601,7 @@
         <v>399</v>
       </c>
       <c r="C199">
-        <v>222.198365452</v>
+        <v>224.02605588</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="100" customHeight="1">
@@ -13876,7 +13612,7 @@
         <v>401</v>
       </c>
       <c r="C200">
-        <v>224.02605588</v>
+        <v>224.044899504</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="100" customHeight="1">
@@ -13898,7 +13634,7 @@
         <v>405</v>
       </c>
       <c r="C202">
-        <v>224.044899504</v>
+        <v>224.120115132</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="100" customHeight="1">
@@ -13909,7 +13645,7 @@
         <v>407</v>
       </c>
       <c r="C203">
-        <v>224.120115132</v>
+        <v>228.057356008</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="100" customHeight="1">
@@ -13920,7 +13656,7 @@
         <v>409</v>
       </c>
       <c r="C204">
-        <v>228.057356008</v>
+        <v>232.182715388</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="100" customHeight="1">
@@ -13931,7 +13667,7 @@
         <v>411</v>
       </c>
       <c r="C205">
-        <v>232.109944372</v>
+        <v>236.120115132</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="100" customHeight="1">
@@ -13942,7 +13678,7 @@
         <v>413</v>
       </c>
       <c r="C206">
-        <v>232.182715388</v>
+        <v>236.1412445</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="100" customHeight="1">
@@ -13953,7 +13689,7 @@
         <v>415</v>
       </c>
       <c r="C207">
-        <v>236.120115132</v>
+        <v>238.084123548</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="100" customHeight="1">
@@ -13964,7 +13700,7 @@
         <v>417</v>
       </c>
       <c r="C208">
-        <v>238.084123548</v>
+        <v>238.135765196</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="100" customHeight="1">
@@ -13975,7 +13711,7 @@
         <v>419</v>
       </c>
       <c r="C209">
-        <v>238.135765196</v>
+        <v>240.078644244</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="100" customHeight="1">
@@ -13986,7 +13722,7 @@
         <v>421</v>
       </c>
       <c r="C210">
-        <v>239.094628656</v>
+        <v>242.094294308</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="100" customHeight="1">
@@ -13997,7 +13733,7 @@
         <v>423</v>
       </c>
       <c r="C211">
-        <v>240.078644244</v>
+        <v>245.037419396</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="100" customHeight="1">
@@ -14008,7 +13744,7 @@
         <v>425</v>
       </c>
       <c r="C212">
-        <v>242.094294308</v>
+        <v>245.944704656</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="100" customHeight="1">
@@ -14019,7 +13755,7 @@
         <v>427</v>
       </c>
       <c r="C213">
-        <v>245.037419396</v>
+        <v>246.198365452</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="100" customHeight="1">
@@ -14030,7 +13766,7 @@
         <v>429</v>
       </c>
       <c r="C214">
-        <v>245.944704656</v>
+        <v>247.983677008</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="100" customHeight="1">
@@ -14041,7 +13777,7 @@
         <v>431</v>
       </c>
       <c r="C215">
-        <v>246.198365452</v>
+        <v>248.02605588</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="100" customHeight="1">
@@ -14052,7 +13788,7 @@
         <v>433</v>
       </c>
       <c r="C216">
-        <v>248.02605588</v>
+        <v>248.214015516</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="100" customHeight="1">
@@ -14063,7 +13799,7 @@
         <v>435</v>
       </c>
       <c r="C217">
-        <v>248.214015516</v>
+        <v>250.22966558</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="100" customHeight="1">
@@ -14074,7 +13810,7 @@
         <v>437</v>
       </c>
       <c r="C218">
-        <v>249.136493468</v>
+        <v>252.099773612</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="100" customHeight="1">
@@ -14085,7 +13821,7 @@
         <v>439</v>
       </c>
       <c r="C219">
-        <v>250.060549568</v>
+        <v>252.13615912</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="100" customHeight="1">
@@ -14096,7 +13832,7 @@
         <v>441</v>
       </c>
       <c r="C220">
-        <v>250.22966558</v>
+        <v>252.172544628</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="100" customHeight="1">
@@ -14107,7 +13843,7 @@
         <v>443</v>
       </c>
       <c r="C221">
-        <v>251.939761508</v>
+        <v>260.214015516</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="100" customHeight="1">
@@ -14118,7 +13854,7 @@
         <v>445</v>
       </c>
       <c r="C222">
-        <v>252.099773612</v>
+        <v>260.214015516</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="100" customHeight="1">
@@ -14129,7 +13865,7 @@
         <v>447</v>
       </c>
       <c r="C223">
-        <v>252.13615912</v>
+        <v>264.245315644</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="100" customHeight="1">
@@ -14140,7 +13876,7 @@
         <v>449</v>
       </c>
       <c r="C224">
-        <v>253.11027872</v>
+        <v>274.0228623200001</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="100" customHeight="1">
@@ -14151,7 +13887,7 @@
         <v>451</v>
       </c>
       <c r="C225">
-        <v>256.032284132</v>
+        <v>274.0605495680001</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="100" customHeight="1">
@@ -14162,7 +13898,7 @@
         <v>453</v>
       </c>
       <c r="C226">
-        <v>259.983677008</v>
+        <v>274.22966558</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="100" customHeight="1">
@@ -14173,7 +13909,7 @@
         <v>455</v>
       </c>
       <c r="C227">
-        <v>260.214015516</v>
+        <v>275.878539012</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="100" customHeight="1">
@@ -14184,7 +13920,7 @@
         <v>457</v>
       </c>
       <c r="C228">
-        <v>260.214015516</v>
+        <v>276.208930136</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="100" customHeight="1">
@@ -14195,7 +13931,7 @@
         <v>459</v>
       </c>
       <c r="C229">
-        <v>263.061614276</v>
+        <v>278.0541624480001</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="100" customHeight="1">
@@ -14206,7 +13942,7 @@
         <v>461</v>
       </c>
       <c r="C230">
-        <v>264.245315644</v>
+        <v>278.2245802</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="100" customHeight="1">
@@ -14217,7 +13953,7 @@
         <v>463</v>
       </c>
       <c r="C231">
-        <v>267.04509162</v>
+        <v>278.260965708</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="100" customHeight="1">
@@ -14228,7 +13964,7 @@
         <v>465</v>
       </c>
       <c r="C232">
-        <v>273.999327072</v>
+        <v>279.991903666</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="100" customHeight="1">
@@ -14239,7 +13975,7 @@
         <v>467</v>
       </c>
       <c r="C233">
-        <v>274.0228623200001</v>
+        <v>284.214015516</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="100" customHeight="1">
@@ -14250,7 +13986,7 @@
         <v>469</v>
       </c>
       <c r="C234">
-        <v>274.0605495680001</v>
+        <v>286.135765196</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="100" customHeight="1">
@@ -14261,7 +13997,7 @@
         <v>471</v>
       </c>
       <c r="C235">
-        <v>274.22966558</v>
+        <v>288.245315644</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="100" customHeight="1">
@@ -14272,7 +14008,7 @@
         <v>473</v>
       </c>
       <c r="C236">
-        <v>276.208930136</v>
+        <v>294.20173658</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="100" customHeight="1">
@@ -14283,7 +14019,7 @@
         <v>475</v>
       </c>
       <c r="C237">
-        <v>278.0541624480001</v>
+        <v>294.255880328</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="100" customHeight="1">
@@ -14294,7 +14030,7 @@
         <v>477</v>
       </c>
       <c r="C238">
-        <v>278.2245802</v>
+        <v>296.214015516</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="100" customHeight="1">
@@ -14305,7 +14041,7 @@
         <v>479</v>
       </c>
       <c r="C239">
-        <v>278.260965708</v>
+        <v>298.0228623200001</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="100" customHeight="1">
@@ -14316,7 +14052,7 @@
         <v>481</v>
       </c>
       <c r="C240">
-        <v>281.060741684</v>
+        <v>315.18344366</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="100" customHeight="1">
@@ -14327,7 +14063,7 @@
         <v>483</v>
       </c>
       <c r="C241">
-        <v>281.060741684</v>
+        <v>326.19133597</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="100" customHeight="1">
@@ -14338,7 +14074,7 @@
         <v>485</v>
       </c>
       <c r="C242">
-        <v>284.214015516</v>
+        <v>330.292265836</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="100" customHeight="1">
@@ -14349,7 +14085,7 @@
         <v>487</v>
       </c>
       <c r="C243">
-        <v>286.135765196</v>
+        <v>332.162783196</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="100" customHeight="1">
@@ -14360,7 +14096,7 @@
         <v>489</v>
       </c>
       <c r="C244">
-        <v>288.245315644</v>
+        <v>335.991654848</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="100" customHeight="1">
@@ -14371,7 +14107,7 @@
         <v>491</v>
       </c>
       <c r="C245">
-        <v>294.20173658</v>
+        <v>338.124527584</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="100" customHeight="1">
@@ -14382,7 +14118,7 @@
         <v>493</v>
       </c>
       <c r="C246">
-        <v>294.255880328</v>
+        <v>344.3079159</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="100" customHeight="1">
@@ -14393,7 +14129,7 @@
         <v>495</v>
       </c>
       <c r="C247">
-        <v>296.214015516</v>
+        <v>352.276615772</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="100" customHeight="1">
@@ -14404,7 +14140,7 @@
         <v>497</v>
       </c>
       <c r="C248">
-        <v>298.0228623200001</v>
+        <v>362.17334788</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="100" customHeight="1">
@@ -14415,7 +14151,7 @@
         <v>499</v>
       </c>
       <c r="C249">
-        <v>315.18344366</v>
+        <v>365.108564468</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="100" customHeight="1">
@@ -14426,7 +14162,7 @@
         <v>501</v>
       </c>
       <c r="C250">
-        <v>330.292265836</v>
+        <v>366.292265836</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="100" customHeight="1">
@@ -14437,7 +14173,7 @@
         <v>503</v>
       </c>
       <c r="C251">
-        <v>335.991654848</v>
+        <v>393.139864596</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="100" customHeight="1">
@@ -14448,73 +14184,7 @@
         <v>505</v>
       </c>
       <c r="C252">
-        <v>338.124527584</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="100" customHeight="1">
-      <c r="A253" t="s">
-        <v>506</v>
-      </c>
-      <c r="B253" t="s">
-        <v>507</v>
-      </c>
-      <c r="C253">
-        <v>344.3079159</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="100" customHeight="1">
-      <c r="A254" t="s">
-        <v>508</v>
-      </c>
-      <c r="B254" t="s">
-        <v>509</v>
-      </c>
-      <c r="C254">
-        <v>348.176167764</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="100" customHeight="1">
-      <c r="A255" t="s">
-        <v>510</v>
-      </c>
-      <c r="B255" t="s">
-        <v>511</v>
-      </c>
-      <c r="C255">
-        <v>365.108564468</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="100" customHeight="1">
-      <c r="A256" t="s">
-        <v>512</v>
-      </c>
-      <c r="B256" t="s">
-        <v>513</v>
-      </c>
-      <c r="C256">
-        <v>393.139864596</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="100" customHeight="1">
-      <c r="A257" t="s">
-        <v>514</v>
-      </c>
-      <c r="B257" t="s">
-        <v>515</v>
-      </c>
-      <c r="C257">
         <v>400.2069860339999</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="100" customHeight="1">
-      <c r="A258" t="s">
-        <v>516</v>
-      </c>
-      <c r="B258" t="s">
-        <v>517</v>
-      </c>
-      <c r="C258">
-        <v>509.220223092</v>
       </c>
     </row>
   </sheetData>
